--- a/American Bedding - CPQ Discussion/American_Bedding_CPQ_Estimate.xlsx
+++ b/American Bedding - CPQ Discussion/American_Bedding_CPQ_Estimate.xlsx
@@ -19,9 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -31,40 +29,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <sz val="10"/>
+      <b val="1"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <sz val="10"/>
+      <color rgb="00008000"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="10"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -73,26 +60,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DAEEF3"/>
-        <bgColor rgb="00DAEEF3"/>
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00548235"/>
-        <bgColor rgb="00548235"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -103,14 +90,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00F4B084"/>
+        <bgColor rgb="00F4B084"/>
       </patternFill>
     </fill>
   </fills>
@@ -136,40 +117,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -537,10 +528,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
@@ -548,7 +539,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>American Bedding -- CPQ Phase 1: Approach Comparison</t>
+          <t>American Bedding -- CPQ: Approach Comparison</t>
         </is>
       </c>
     </row>
@@ -560,7 +551,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Recommended: HubSpot CPQ + n8n Middleware</t>
+          <t>Recommended: HubSpot CPQ + Hybrid Architecture</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -577,7 +568,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>HubSpot becomes the quoting interface. n8n middleware orchestrates product data from NetSuite, freight rates from Kuebix, and dynamic weight calculations. Reps create and manage quotes without leaving HubSpot.</t>
+          <t>HubSpot becomes the quoting interface. HubSpot custom code actions handle lightweight triggers. A dedicated cloud API (Railway) orchestrates product data from NetSuite, freight rates from Kuebix, and dynamic weight calculations. Reps create and manage quotes without leaving HubSpot.</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -587,17 +578,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>$34,500 fixed fee</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1 (V1): ~$30,000 | Phase 2 (V2): ~$11,500 | Total: ~$41,500</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>~$18,000-$22,000 (reduced scope)</t>
         </is>
@@ -621,17 +612,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Freight Automation</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Full -- Kuebix API via n8n with dynamic weight calculation. Multi-carrier LTL rate shopping automated.</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Full -- Kuebix API with dynamic weight calculation. Multi-carrier LTL rate shopping automated. Phase 1 via HubSpot custom code, Phase 2 migrates to production API for unlimited execution time.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>None or partial -- manual Kuebix entry continues, or NetSuite-side integration (TPI scope).</t>
         </is>
@@ -645,7 +636,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Dynamic engine in n8n replicates Excel formula logic for all 5 product lines. Handles custom sizes.</t>
+          <t>Dynamic engine replicates Excel formula logic for all 5 product lines. Handles custom sizes. Validated: no VBA, no macros, no external refs. Dorm Mattress is highest complexity (9-level nesting, 180+ paths).</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -655,17 +646,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>NetSuite Integration</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Bi-directional: product catalog sync, quote-to-estimate creation, estimate-to-sales-order conversion, credit hold check.</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Enhanced one-way: quote visibility in HubSpot. No quote creation from HubSpot.</t>
         </is>
@@ -679,7 +670,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Automated -- n8n determines correct warehouse origin per product/order for Kuebix API calls.</t>
+          <t>Automated -- system determines correct warehouse origin per product/order for Kuebix API calls.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -689,17 +680,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM -- 3-system integration through n8n middleware. Kuebix API fully reviewed. Dynamic weight calc is highest-risk workstream.</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>MEDIUM -- 3-system integration. Kuebix API fully reviewed. Excel calculators validated. HubSpot 20s timeout is Phase 1 limitation, eliminated in Phase 2.</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>LOW -- simpler scope but does not solve the core pain point (4-system juggling).</t>
         </is>
@@ -723,17 +714,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Payback Period</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>7-9 months on labor savings alone</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Phase 1: 6-8 months on labor savings alone</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>12-18 months (visibility value harder to quantify)</t>
         </is>
@@ -742,39 +733,54 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 Readiness</t>
+          <t>Production Readiness</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>Phase 2 delivers production-grade codebase: version-controlled, unit-tested, CI/CD deployed. Maintainable by any developer.</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Minimal -- limited integration means less production code to maintain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Future Phase Readiness</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
           <t>Strong foundation for government RFP automation, customer configurator, and external storefront.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Minimal -- Phase 2 would still need to move quoting to HubSpot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Minimal -- future phase would still need to move quoting to HubSpot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>HubSpot CPQ + n8n Middleware is recommended. The core pain point is 4-system juggling that costs Caleb 10-60 minutes per quote across 65 quotes/week. The alternative (enhanced visibility) does not reduce that workload -- it only lets leadership see what is happening. The recommended approach eliminates the system-jumping entirely, automates the freight calculation that is the single biggest time sink, and builds the foundation for Phase 2 government RFP automation. The Kuebix API has been fully reviewed and the integration path is well-defined. The dynamic weight calculation engine is the highest-risk workstream -- getting the Excel spreadsheets from Caleb before finalizing the engagement is critical.</t>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>HubSpot CPQ with hybrid architecture is recommended. The core pain point is 4-system juggling that costs Caleb 10-60 minutes per quote across 65 quotes/week. The alternative (enhanced visibility) does not reduce that workload. The recommended approach eliminates system-jumping entirely, automates freight calculation, and builds the foundation for future phases. Two-phase delivery gets reps quoting in HubSpot fast (Phase 1) then hardens the platform for long-term reliability (Phase 2). The Kuebix API and Excel calculators have both been fully reviewed and validated.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
+  <mergeCells count="1">
+    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -786,31 +792,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Hourly Rate:</t>
         </is>
       </c>
-      <c r="B1" s="8" t="n">
+      <c r="B1" t="n">
         <v>150</v>
       </c>
     </row>
@@ -865,116 +871,86 @@
           <t>Notes / Assumptions</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>Actual Hours</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>Actual Cost</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>PHASE 1 (V1): HUBSPOT-NATIVE CPQ</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>HubSpot CPQ Architecture &amp; Configuration</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Configure Commerce Hub CPQ module. Custom deal/quote/line item properties. Quote approval workflows. Quote numbering and validity settings (30-day window). Payment terms configuration (prepay, net 10/30/60).</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C5" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="E4" s="3">
-        <f>AVERAGE(C4,D4)</f>
-        <v/>
-      </c>
-      <c r="F4" s="3">
+      <c r="E5" s="3">
+        <f>AVERAGE(C5,D5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="3">
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G4" s="10">
-        <f>C4*$B$1</f>
-        <v/>
-      </c>
-      <c r="H4" s="10">
-        <f>D4*$B$1</f>
-        <v/>
-      </c>
-      <c r="I4" s="10">
-        <f>E4*$B$1</f>
-        <v/>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="G5" s="3">
+        <f>C5*$B$1</f>
+        <v/>
+      </c>
+      <c r="H5" s="3">
+        <f>D5*$B$1</f>
+        <v/>
+      </c>
+      <c r="I5" s="3">
+        <f>E5*$B$1</f>
+        <v/>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Commerce Hub Professional confirmed. Standard CPQ config with custom properties for manufacturing context. Approval workflows for discount overrides.</t>
         </is>
       </c>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="12" t="n"/>
-      <c r="M4" s="11">
-        <f>IF(K4="","",K4-E4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Product Catalog Sync (NetSuite to HubSpot)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>SuiteQL extraction of 700 SKUs from NetSuite. Map to HubSpot products with custom properties: weight components, freight class, dimensions (L x W x H), cover type, foam series, construction type. Build n8n scheduled sync for ongoing price and product updates.</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="E5" s="4">
-        <f>AVERAGE(C5,D5)</f>
-        <v/>
-      </c>
-      <c r="F5" s="4">
-        <f>$B$1</f>
-        <v/>
-      </c>
-      <c r="G5" s="13">
-        <f>C5*$B$1</f>
-        <v/>
-      </c>
-      <c r="H5" s="13">
-        <f>D5*$B$1</f>
-        <v/>
-      </c>
-      <c r="I5" s="13">
-        <f>E5*$B$1</f>
-        <v/>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Flat catalog approach -- one product per SKU, custom properties for filtering. SuiteQL batch queries efficient (1-2 API calls for full catalog). Ongoing sync handles NetSuite price changes. OAuth 2.0 M2M auth.</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="n"/>
-      <c r="L5" s="12" t="n"/>
-      <c r="M5" s="11">
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9">
         <f>IF(K5="","",K5-E5)</f>
         <v/>
       </c>
@@ -982,19 +958,19 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>NetSuite Quote-to-Order Integration</t>
+          <t>Product Catalog Sync (NetSuite to HubSpot)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>OAuth 2.0 M2M setup in NetSuite. Quote acceptance triggers NetSuite Estimate creation via REST API. Estimate-to-Sales Order conversion on fulfillment. Customer credit status check before quoting. Payment terms sync. Price level sync from NetSuite.</t>
+          <t>SuiteQL extraction of 700 SKUs from NetSuite. Map to HubSpot products with custom properties: weight components, freight class, dimensions (L x W x H), cover type, foam series, construction type. HubSpot custom code sync trigger for ongoing price and product updates.</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E6" s="3">
         <f>AVERAGE(C6,D6)</f>
@@ -1004,75 +980,75 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="3">
         <f>C6*$B$1</f>
         <v/>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="3">
         <f>D6*$B$1</f>
         <v/>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="3">
         <f>E6*$B$1</f>
         <v/>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Bi-directional: HubSpot quote -&gt; NetSuite estimate -&gt; sales order -&gt; work order. Customer credit hold check reads AR data before allowing quote. 1.25x ERP adjacency premium applied (existing integration, not greenfield).</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="n"/>
-      <c r="L6" s="12" t="n"/>
-      <c r="M6" s="11">
+          <t>Flat catalog -- one product per SKU. SuiteQL batch queries (1-2 API calls). HubSpot custom code trigger replaces n8n scheduled sync. OAuth 2.0 M2M auth.</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="n"/>
+      <c r="L6" s="9" t="n"/>
+      <c r="M6" s="9">
         <f>IF(K6="","",K6-E6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Kuebix Freight Integration + Origin Routing</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>n8n workflow: collect line item weights and dimensions from quote -&gt; determine origin warehouse based on product/order rules -&gt; POST /action/quickRate to Kuebix -&gt; parse multi-carrier LTL response -&gt; write cheapest rate as freight line item on quote. Manual override option. Error handling with fallback to manual entry.</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>NetSuite Quote-to-Order Integration</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>OAuth 2.0 M2M setup. Quote acceptance triggers NetSuite Estimate creation via HubSpot custom code -&gt; REST API. Estimate-to-Sales Order conversion. Customer credit hold check. Payment terms sync. Price level sync.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D7" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3">
         <f>AVERAGE(C7,D7)</f>
         <v/>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="3">
         <f>C7*$B$1</f>
         <v/>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="3">
         <f>D7*$B$1</f>
         <v/>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="3">
         <f>E7*$B$1</f>
         <v/>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>Kuebix API fully reviewed (OpenAPI 3.0.2). Basic Auth. quickRate returns multi-carrier quotes sorted by price. Full street address required (not just zip). Origin routing adds complexity for multiple warehouse locations. persist=false prevents phantom shipments.</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="n"/>
-      <c r="L7" s="12" t="n"/>
-      <c r="M7" s="11">
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Bi-directional: HubSpot quote -&gt; NetSuite estimate -&gt; sales order -&gt; work order. Credit hold reads AR data. 1.25x ERP adjacency premium (existing integration). HubSpot custom code handles orchestration.</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="9" t="n"/>
+      <c r="M7" s="9">
         <f>IF(K7="","",K7-E7)</f>
         <v/>
       </c>
@@ -1080,19 +1056,19 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Dynamic Weight Calculation Engine</t>
+          <t>Kuebix Freight Integration + Origin Routing</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Replicate Excel formula logic in n8n for all 5 product lines: Dorm Mattress, Camp Mattress, Dura-Last Poly-Fiber, SoFlux OX Covers, Vinyl Covers. Panel calculations, fabric weight by cover type (Anti-Bac Vinyl 283.5 g/yd2, SoFlux OX 121.9 g/yd2, Pinstripe 102.1 g/yd2), foam weight by density/thickness, innerspring weight by size, cotton batting, insulator pad, packaging weight. Cube volume for LTL/TL determination. Validate against known Excel outputs.</t>
+          <t>HubSpot custom code: collect line item weights/dims -&gt; determine origin warehouse -&gt; POST /action/quickRate to Kuebix -&gt; parse multi-carrier LTL response -&gt; write cheapest rate as freight line item. Manual override option. Error handling with fallback.</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E8" s="3">
         <f>AVERAGE(C8,D8)</f>
@@ -1102,75 +1078,75 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="3">
         <f>C8*$B$1</f>
         <v/>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="3">
         <f>D8*$B$1</f>
         <v/>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="3">
         <f>E8*$B$1</f>
         <v/>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>HIGHEST-RISK WORKSTREAM. 5 separate Excel spreadsheets with nested IF/AND formulas. Each product line has different calculation paths. Must get Excel files from Caleb and verify no VBA/macros before committing. Test formula replication on 3 product lines before building all 5.</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="n"/>
-      <c r="L8" s="12" t="n"/>
-      <c r="M8" s="11">
+          <t>Kuebix API fully reviewed (OpenAPI 3.0.2). Basic Auth. quickRate returns multi-carrier quotes. Full street address required. Origin routing for multiple warehouses. persist=false prevents phantom shipments. 20s HubSpot timeout risk for multi-line quotes.</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="9">
         <f>IF(K8="","",K8-E8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Quote Template Design</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Custom HubL/HTML/CSS quote template matching current NetSuite quote format. Line item table (Qty, Item #, Description, Unit Price, Amount). Subtotal, volume discount (10%), state-based tax, shipping line, total. Damaged freight policy terms. Delivery instructions field. Customer acceptance flow (clickwrap or e-sign). PDF optimization.</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Dynamic Weight Calculation Engine</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Replicate Excel formula logic in HubSpot custom code for all 5 product lines: Dorm Mattress, Camp Mattress, Dura-Last Poly-Fiber, SoFlux OX Covers, Vinyl Covers. Panel calcs, fabric weight by cover type, foam weight by density/thickness, innerspring weight by size, batting, insulator pad, packaging. Cube volume for LTL/TL determination.</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="E9" s="3">
         <f>AVERAGE(C9,D9)</f>
         <v/>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="3">
         <f>C9*$B$1</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="3">
         <f>D9*$B$1</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="3">
         <f>E9*$B$1</f>
         <v/>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Reference: 5 NetSuite PDF quote examples provided. Must match header/footer, line item format, terms section. HubSpot Flow theme supports custom properties in line item table. @media print CSS for PDF generation.</t>
-        </is>
-      </c>
-      <c r="K9" s="11" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="11">
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>HIGHEST-COMPLEXITY WORKSTREAM. Validated 2026-04-04: no VBA, no external refs, no circular formulas. Dorm (HIGH -- 9-level nesting, 180+ paths), Camp (MED -- 48+ paths), Dura-Last (MED -- 12+ paths), SoFlux OX/Vinyl (LOW -- ~80% reuse). Open: 'Special Case Check with Delbert' in Dorm Mattress.</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="n"/>
+      <c r="L9" s="9" t="n"/>
+      <c r="M9" s="9">
         <f>IF(K9="","",K9-E9)</f>
         <v/>
       </c>
@@ -1178,19 +1154,19 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Discount, Tax &amp; Payment Terms Logic</t>
+          <t>Quote Template Design</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Volume discount automation (10% threshold -- confirm if automatic or requires approval above certain levels). State-based tax calculation (9.75% TN, exempt for out-of-state -- may need broader state tax table). Payment terms workflow (prepay for new customers, net 10/30/60 for established). Credit hold check integration from NetSuite AR data.</t>
+          <t>Custom HubL/HTML/CSS quote template matching current NetSuite format. Line item table (Qty, Item #, Description, Unit Price, Amount). Subtotal, volume discount (10%), state-based tax, shipping line, total. Damaged freight policy terms. Customer acceptance flow. PDF optimization.</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E10" s="3">
         <f>AVERAGE(C10,D10)</f>
@@ -1200,75 +1176,75 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="3">
         <f>C10*$B$1</f>
         <v/>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="3">
         <f>D10*$B$1</f>
         <v/>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="3">
         <f>E10*$B$1</f>
         <v/>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Tax logic may need external service for multi-state accuracy beyond TN. Discount approval thresholds TBD at kickoff. Credit hold is a read from NetSuite customer record -- flags but does not hard-block.</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="n"/>
-      <c r="L10" s="12" t="n"/>
-      <c r="M10" s="11">
+          <t>Reference: 5 NetSuite PDF examples. Must match header/footer, line item format, terms. HubSpot Flow theme supports custom properties. @media print CSS for PDF.</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="9">
         <f>IF(K10="","",K10-E10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Training &amp; Documentation</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Sales team training (Caleb, Don): new HubSpot quoting workflow, product selection, freight review. Admin training (Sarah-Beth, Patrick): system management, product catalog updates, sync monitoring, troubleshooting. All sessions virtual and recorded. Admin guide + user quick reference card.</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Discount, Tax &amp; Payment Terms Logic</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Volume discount automation (10% threshold). State-based tax calculation (9.75% TN, exempt OOS). Payment terms workflow (prepay/net 10/30/60). Credit hold integration from NetSuite AR. All via HubSpot custom code.</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="D11" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" s="3">
         <f>AVERAGE(C11,D11)</f>
         <v/>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="3">
         <f>C11*$B$1</f>
         <v/>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="3">
         <f>D11*$B$1</f>
         <v/>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="3">
         <f>E11*$B$1</f>
         <v/>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>2-3 sessions total. Emphasis on showing reps the time savings. Admin guide covers n8n workflow monitoring and product sync management. Record for future onboarding.</t>
-        </is>
-      </c>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="11">
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Tax may need external service for multi-state. Discount approval thresholds TBD at kickoff. Credit hold is read from NetSuite -- flags but does not hard-block. Fits within HubSpot custom code 20s limit.</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9">
         <f>IF(K11="","",K11-E11)</f>
         <v/>
       </c>
@@ -1276,19 +1252,19 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Testing &amp; QA</t>
+          <t>Training &amp; Documentation</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>End-to-end integration testing across all 3 systems. Quote accuracy validation (compare HubSpot output to known NetSuite quotes from the 5 examples). Weight calculation validation (compare n8n output to Excel calculators). Freight calculation validation (compare n8n/Kuebix output to manual Kuebix lookups). UAT with Caleb and Don. 2-week hypercare post go-live.</t>
+          <t>Sales training (Caleb, Don): quoting workflow, product selection, freight review. Admin training (Sarah-Beth, Patrick): system management, catalog updates, sync monitoring. All virtual, recorded. Admin guide + user quick reference card.</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E12" s="3">
         <f>AVERAGE(C12,D12)</f>
@@ -1298,139 +1274,674 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="3">
         <f>C12*$B$1</f>
         <v/>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="3">
         <f>D12*$B$1</f>
         <v/>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="3">
         <f>E12*$B$1</f>
         <v/>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Test matrix covers: product sync accuracy, weight calc per product line, freight quote accuracy, quote template rendering, NetSuite estimate creation, sales order conversion, credit hold flagging. 2 UAT sessions minimum.</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="n"/>
-      <c r="L12" s="12" t="n"/>
-      <c r="M12" s="11">
+          <t>2-3 sessions. Emphasis on time savings. Admin guide covers HubSpot custom code monitoring and product sync. Record for onboarding.</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="n"/>
+      <c r="L12" s="9" t="n"/>
+      <c r="M12" s="9">
         <f>IF(K12="","",K12-E12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Testing &amp; QA</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>E2E integration testing across all 3 systems. Quote accuracy vs. NetSuite examples. Weight calc vs. Excel baselines. Freight vs. manual Kuebix lookups. UAT with Caleb and Don. 2-week hypercare.</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" s="3">
+        <f>AVERAGE(C13,D13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="3">
+        <f>$B$1</f>
+        <v/>
+      </c>
+      <c r="G13" s="3">
+        <f>C13*$B$1</f>
+        <v/>
+      </c>
+      <c r="H13" s="3">
+        <f>D13*$B$1</f>
+        <v/>
+      </c>
+      <c r="I13" s="3">
+        <f>E13*$B$1</f>
+        <v/>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Test matrix: product sync accuracy, weight calc per product line, freight quote accuracy, template rendering, NetSuite estimate creation, SO conversion, credit hold. 2 UAT sessions. Dorm Mattress sampling strategy for 180+ paths.</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="n"/>
+      <c r="L13" s="9" t="n"/>
+      <c r="M13" s="9">
+        <f>IF(K13="","",K13-E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Project Management</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Kickoff meeting, weekly status calls, milestone reviews. Coordination with American Bedding team (Mike, Sarah-Beth, Caleb, Patrick). Documentation and change request management. Scope creep prevention (especially government RFP boundary). Go-live planning.</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Kickoff, weekly syncs, milestone reviews. Coordination with American Bedding team. Documentation and change request management. Scope creep prevention. Go-live planning.</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="D13" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="E13" s="4">
-        <f>AVERAGE(C13,D13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="4">
+      <c r="D14" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E14" s="3">
+        <f>AVERAGE(C14,D14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="3">
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G13" s="13">
-        <f>C13*$B$1</f>
-        <v/>
-      </c>
-      <c r="H13" s="13">
-        <f>D13*$B$1</f>
-        <v/>
-      </c>
-      <c r="I13" s="13">
-        <f>E13*$B$1</f>
-        <v/>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>~12% of total hours. Weekly syncs with Sarah-Beth (primary POC). Milestone reviews with Mike/Patrick at weeks 4, 8, and go-live. All change requests documented formally.</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="12" t="n"/>
-      <c r="M13" s="11">
-        <f>IF(K13="","",K13-E13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C14" s="15">
-        <f>SUM(C4:C13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="15">
-        <f>SUM(D4:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="15">
-        <f>SUM(E4:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="14">
+      <c r="G14" s="3">
+        <f>C14*$B$1</f>
+        <v/>
+      </c>
+      <c r="H14" s="3">
+        <f>D14*$B$1</f>
+        <v/>
+      </c>
+      <c r="I14" s="3">
+        <f>E14*$B$1</f>
+        <v/>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>~10% of total. Weekly syncs with Sarah-Beth. Milestone reviews at weeks 4, 8, and go-live. All change requests documented.</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="n"/>
+      <c r="L14" s="9" t="n"/>
+      <c r="M14" s="9">
+        <f>IF(K14="","",K14-E14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>PHASE 1 SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11">
+        <f>SUM(C5:C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="11">
+        <f>SUM(D5:D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>SUM(E5:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="11">
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G14" s="16">
-        <f>SUM(G4:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="16">
-        <f>SUM(H4:H13)</f>
-        <v/>
-      </c>
-      <c r="I14" s="16">
-        <f>SUM(I4:I13)</f>
-        <v/>
-      </c>
-      <c r="K14" s="11">
-        <f>SUM(K4:K13)</f>
-        <v/>
-      </c>
-      <c r="L14" s="12">
-        <f>SUM(L4:L13)</f>
-        <v/>
-      </c>
-      <c r="M14" s="11" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>FIXED FEE PRESENTED:</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="n">
-        <v>34500</v>
-      </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="G15" s="11">
+        <f>SUM(G5:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="11">
+        <f>SUM(H5:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="11">
+        <f>SUM(I5:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="11">
+        <f>SUM(K5:K14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="11">
+        <f>SUM(L5:L14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>PHASE 2 (V2): RAILWAY PRODUCTION PLATFORM</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="13" t="n"/>
+      <c r="J17" s="13" t="n"/>
+      <c r="K17" s="13" t="n"/>
+      <c r="L17" s="13" t="n"/>
+      <c r="M17" s="13" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Railway Infrastructure Setup</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Production API project setup on Railway. CI/CD pipeline (git push deploy). Environment config (staging + production). Health monitoring endpoints. Error logging and alerting. Security hardening.</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" s="3">
+        <f>AVERAGE(C18,D18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="3">
+        <f>$B$1</f>
+        <v/>
+      </c>
+      <c r="G18" s="3">
+        <f>C18*$B$1</f>
+        <v/>
+      </c>
+      <c r="H18" s="3">
+        <f>D18*$B$1</f>
+        <v/>
+      </c>
+      <c r="I18" s="3">
+        <f>E18*$B$1</f>
+        <v/>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Railway provides managed hosting with auto-deploy from git. Node.js or Python runtime. Environment variables for secrets (API keys, OAuth tokens). Health check endpoint for uptime monitoring.</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="n"/>
+      <c r="L18" s="9" t="n"/>
+      <c r="M18" s="9">
+        <f>IF(K18="","",K18-E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Weight Engine Migration</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Migrate all 5 product-line calculators from HubSpot custom code to Railway API. Refactor into modular, testable JavaScript/Python modules. Add comprehensive unit test coverage for all calculation paths. Dorm Mattress sampling strategy for 180+ paths.</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E19" s="3">
+        <f>AVERAGE(C19,D19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="3">
+        <f>$B$1</f>
+        <v/>
+      </c>
+      <c r="G19" s="3">
+        <f>C19*$B$1</f>
+        <v/>
+      </c>
+      <c r="H19" s="3">
+        <f>D19*$B$1</f>
+        <v/>
+      </c>
+      <c r="I19" s="3">
+        <f>E19*$B$1</f>
+        <v/>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Code already exists from Phase 1 -- migration is refactor + test coverage. Dorm Mattress needs ~20 representative test cases covering 80% of paths. SoFlux/Vinyl share ~80% code. Target: 100% coverage for critical paths.</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="n"/>
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="9">
+        <f>IF(K19="","",K19-E19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Kuebix Freight Migration</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Migrate Kuebix quickRate orchestration to Railway API. Multi-line, multi-carrier quote assembly without timeout risk. Retry logic for carrier API failures. Response caching for repeat origin/destination/weight combos.</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E20" s="3">
+        <f>AVERAGE(C20,D20)</f>
+        <v/>
+      </c>
+      <c r="F20" s="3">
+        <f>$B$1</f>
+        <v/>
+      </c>
+      <c r="G20" s="3">
+        <f>C20*$B$1</f>
+        <v/>
+      </c>
+      <c r="H20" s="3">
+        <f>D20*$B$1</f>
+        <v/>
+      </c>
+      <c r="I20" s="3">
+        <f>E20*$B$1</f>
+        <v/>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Eliminates HubSpot 20s timeout constraint. Retry logic handles intermittent Kuebix API failures gracefully. Cache reduces API calls for repeat shipping lanes.</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="n"/>
+      <c r="L20" s="9" t="n"/>
+      <c r="M20" s="9">
+        <f>IF(K20="","",K20-E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>NetSuite Integration Migration</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Migrate NetSuite OAuth token management, catalog sync, and quote-to-order flow to Railway. Automated catalog sync via Railway cron. Proper error handling and retry for REST API calls.</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" s="3">
+        <f>AVERAGE(C21,D21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="3">
+        <f>$B$1</f>
+        <v/>
+      </c>
+      <c r="G21" s="3">
+        <f>C21*$B$1</f>
+        <v/>
+      </c>
+      <c r="H21" s="3">
+        <f>D21*$B$1</f>
+        <v/>
+      </c>
+      <c r="I21" s="3">
+        <f>E21*$B$1</f>
+        <v/>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>OAuth 2.0 M2M token refresh automated. SuiteQL catalog extraction runs on schedule (Railway cron). Estimate/SO creation with retry. Full audit logging.</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="n"/>
+      <c r="L21" s="9" t="n"/>
+      <c r="M21" s="9">
+        <f>IF(K21="","",K21-E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>HubSpot Rewiring</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Update HubSpot custom code actions to call Railway API endpoints instead of running logic locally. HubSpot becomes a thin trigger layer. Webhook configuration.</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" s="3">
+        <f>AVERAGE(C22,D22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="3">
+        <f>$B$1</f>
+        <v/>
+      </c>
+      <c r="G22" s="3">
+        <f>C22*$B$1</f>
+        <v/>
+      </c>
+      <c r="H22" s="3">
+        <f>D22*$B$1</f>
+        <v/>
+      </c>
+      <c r="I22" s="3">
+        <f>E22*$B$1</f>
+        <v/>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Simple HTTP calls from HubSpot custom code to Railway API. Minimal logic in HubSpot -- just trigger + response handling. Reduces HubSpot custom code complexity significantly.</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="n"/>
+      <c r="L22" s="9" t="n"/>
+      <c r="M22" s="9">
+        <f>IF(K22="","",K22-E22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Integration &amp; Regression Testing</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Full regression suite: every Phase 1 workflow operates identically on Railway. Load testing at 65+ quotes/week. Performance benchmarking. Documentation update.</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E23" s="3">
+        <f>AVERAGE(C23,D23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="3">
+        <f>$B$1</f>
+        <v/>
+      </c>
+      <c r="G23" s="3">
+        <f>C23*$B$1</f>
+        <v/>
+      </c>
+      <c r="H23" s="3">
+        <f>D23*$B$1</f>
+        <v/>
+      </c>
+      <c r="I23" s="3">
+        <f>E23*$B$1</f>
+        <v/>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Regression against Phase 1 baseline ensures zero behavior change. Load test confirms production volume capacity. Updated admin guide and architecture docs.</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="9" t="n"/>
+      <c r="M23" s="9">
+        <f>IF(K23="","",K23-E23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Project Management</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Milestone reviews, documentation updates, Phase 2 close-out.</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" s="3">
+        <f>AVERAGE(C24,D24)</f>
+        <v/>
+      </c>
+      <c r="F24" s="3">
+        <f>$B$1</f>
+        <v/>
+      </c>
+      <c r="G24" s="3">
+        <f>C24*$B$1</f>
+        <v/>
+      </c>
+      <c r="H24" s="3">
+        <f>D24*$B$1</f>
+        <v/>
+      </c>
+      <c r="I24" s="3">
+        <f>E24*$B$1</f>
+        <v/>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Lighter PM load than Phase 1. ~10% of Phase 2 hours.</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="9" t="n"/>
+      <c r="M24" s="9">
+        <f>IF(K24="","",K24-E24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>PHASE 2 SUBTOTAL</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11">
+        <f>SUM(C18:C24)</f>
+        <v/>
+      </c>
+      <c r="D25" s="11">
+        <f>SUM(D18:D24)</f>
+        <v/>
+      </c>
+      <c r="E25" s="11">
+        <f>SUM(E18:E24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="11">
+        <f>$B$1</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
+        <f>SUM(G18:G24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="11">
+        <f>SUM(H18:H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="11">
+        <f>SUM(I18:I24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="11" t="n"/>
+      <c r="K25" s="11">
+        <f>SUM(K18:K24)</f>
+        <v/>
+      </c>
+      <c r="L25" s="11">
+        <f>SUM(L18:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="11" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>GRAND TOTAL</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15">
+        <f>C15+C25</f>
+        <v/>
+      </c>
+      <c r="D27" s="15">
+        <f>D15+D25</f>
+        <v/>
+      </c>
+      <c r="E27" s="15">
+        <f>E15+E25</f>
+        <v/>
+      </c>
+      <c r="F27" s="15">
+        <f>$B$1</f>
+        <v/>
+      </c>
+      <c r="G27" s="15">
+        <f>G15+G25</f>
+        <v/>
+      </c>
+      <c r="H27" s="15">
+        <f>H15+H25</f>
+        <v/>
+      </c>
+      <c r="I27" s="15">
+        <f>I15+I25</f>
+        <v/>
+      </c>
+      <c r="J27" s="15" t="n"/>
+      <c r="K27" s="15">
+        <f>K15+K25</f>
+        <v/>
+      </c>
+      <c r="L27" s="15">
+        <f>L15+L25</f>
+        <v/>
+      </c>
+      <c r="M27" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 1 FIXED FEE:</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Fixed fee. Client sees this number only -- no hours breakdown in proposal.</t>
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 2 FIXED FEE:</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>11500</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Fixed fee. Separate SOW or Phase 2 addendum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>COMBINED FIXED FEE:</t>
+        </is>
+      </c>
+      <c r="I31" s="16">
+        <f>I29+I30</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A4:J4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1441,17 +1952,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1497,402 +2008,491 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="17" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>HubSpot custom code 20-second execution timeout for complex multi-line quotes</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Multi-product quotes requiring weight calc + Kuebix API call may approach or exceed 20s limit. Quote fails to generate freight line item.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Test with largest known quote configurations in Phase 1. Manual fallback for edge cases. Phase 2 eliminates this risk entirely by migrating to Railway API (no execution limits).</t>
+        </is>
+      </c>
+      <c r="G2" s="17" t="inlineStr">
+        <is>
+          <t>Consultant</t>
+        </is>
+      </c>
+      <c r="H2" s="17" t="inlineStr">
+        <is>
+          <t>Open -- Phase 1 risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Excel weight calculator edge cases -- 'Special Case Check with Delbert' in Dorm Mattress</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Undocumented business logic in Dorm Mattress calculator. #VALUE! errors noted. Edge cases may produce incorrect weights for specific configurations.</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Clarify with Caleb/Delbert at kickoff. Build Dorm Mattress calculator first. Sampling strategy for 180+ paths (~20 representative test cases covering 80% of paths). Validate against known weights.</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>Consultant + Caleb</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>NetSuite data quality -- SKU duplicates, stale pricing, missing attributes from Jan 2026 launch</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Product sync imports bad data into HubSpot. Quotes show wrong prices or descriptions. Customer trust eroded.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>NetSuite item data audit during Week 1. Define cleanup scope before building sync. SuiteQL queries validate data quality before bulk import. Flag items missing required fields.</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Consultant + Sarah-Beth</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Scope creep via Vesco/Kaitlynn relationship -- government RFP work creeps into Phase 1</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Informal requests bypass SOW. Government-specific requirements consume hours budgeted for CPQ. Don Reynolds enthusiasm for future phases pulls scope.</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>SOW signed by Mike Taylor or Patrick (budget authority). Phase boundaries iron-clad in SOW. All change requests documented. Weekly hours tracking visible to client.</t>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
+        <is>
+          <t>Kyle + Mike</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>NetSuite still stabilizing (launched Jan 1, 2026) -- API schema changes, TPI updates</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Integration breaks after TPI makes changes. Data model shifts invalidate SuiteQL queries. API access disrupted during maintenance.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Build against documented REST API (not custom SuiteScript). Version-lock API endpoints. Establish communication channel with TPI for change notifications.</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>Consultant</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Multiple shipping origins -- wrong origin = wrong freight = wrong price</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Incorrect origin address sent to Kuebix. Freight quotes are wrong. Customer receives inaccurate pricing. Trust and margin impact.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Map all warehouse addresses at kickoff. Define explicit routing rules. Test each origin with known Kuebix quotes. Default origin fallback if routing is ambiguous.</t>
+        </is>
+      </c>
+      <c r="G7" s="17" t="inlineStr">
+        <is>
+          <t>Consultant + Mike</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>HubSpot CPQ limitations -- no calculated fields, no product variants, no native tax engine</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Workarounds needed for freight as line item (must be pre-computed). Product selection UX is less polished than dedicated CPQ. Tax calculation requires external logic.</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Pre-compute all calculated values in custom code before quote is published. Use custom properties and filtered views for product selection. Tax logic in Ops Hub custom code.</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>Consultant</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Kuebix API rate limits undocumented -- high quote volume could hit throttling</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>65 quotes/week plus revisions could exceed undocumented rate limits. Freight quotes fail or are throttled.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Confirm rate limits with Kuebix support. Implement response caching for repeat shipping lanes (Phase 2). Graceful fallback to manual entry.</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>Consultant</t>
+        </is>
+      </c>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Adoption risk -- sales reps switching from NetSuite quoting to HubSpot quoting</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Caleb and Don revert to old process. New system goes unused. ROI unrealized.</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Executive mandate from Mike. Show concrete time savings in training. 2-week parallel run. Monitor adoption metrics. Caleb is motivated (described the pain).</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>Mike + Consultant</t>
+        </is>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Freight class determination per product is unclear or inconsistent</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Wrong freight class to Kuebix. Shipping costs systematically over or under estimated. Margin impact across all quotes.</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Confirm freight class source at kickoff. Document per product line. Validate against known Kuebix quotes.</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="inlineStr">
+        <is>
+          <t>Consultant + Caleb</t>
+        </is>
+      </c>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Budget authority anchored on Billy $25K verbal benchmark -- two-phase total of ~$41.5K creates sticker shock</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Patrick (CFO) expects $25K. Phase 1 at ~$30K may trigger budget negotiation.</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Frame $25K as pre-discovery estimate. Phase 1 at ~$30K is closer to anchor than previous $34.5K. Two-phase reduces upfront commitment. Value-based ROI framing: Phase 1 pays back in 6-8 months. Phase 2 is a natural follow-on after reps see value.</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>Kyle + Billy</t>
+        </is>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
           <t>Excel weight calculator logic more complex than analyzed -- VBA macros, external references, or circular formulas</t>
         </is>
       </c>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Dynamic weight engine blows past 44 hrs max estimate. Fixed fee becomes untenable. Workstream 5 is unbounded.</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Get all 5 Excel files from Caleb BEFORE finalizing engagement. Test formula replication on Dorm Mattress calculator first (most complex). If VBA or external refs found, re-scope as time-and-materials for weight engine only.</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Kyle (pre-engagement)</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>NetSuite data quality -- SKU duplicates, stale pricing, missing attributes from Jan 2026 launch</t>
-        </is>
-      </c>
-      <c r="C3" s="19" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Product sync imports bad data into HubSpot. Quotes show wrong prices or descriptions. Customer trust eroded.</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>NetSuite item data audit during Week 1. Define cleanup scope before building sync. SuiteQL queries validate data quality before bulk import. Flag items missing required fields (weight, freight class, dimensions).</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Consultant + Sarah-Beth</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Scope creep via Vesco/Kaitlynn relationship -- government RFP work creeps into Phase 1</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Informal requests bypass SOW. Government-specific requirements consume hours budgeted for CPQ. Don Reynolds enthusiasm for Phase 2 pulls scope.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>SOW signed by Mike Taylor or Patrick (budget authority), not Kaitlynn. Phase 1/Phase 2 boundary iron-clad in SOW. All change requests documented formally. Weekly hours tracking visible to client.</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Kyle + Mike</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>NetSuite still stabilizing (launched Jan 1, 2026) -- API schema changes, TPI updates, data quality shifts</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Integration breaks after TPI makes changes. Data model shifts invalidate SuiteQL queries. API access disrupted during maintenance.</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Build integration against documented REST API (not custom SuiteScript). Version-lock API endpoints. Establish communication channel with TPI for change notifications even though they are not directly involved.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Consultant</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Multiple shipping origins add routing complexity -- wrong origin = wrong freight quote = wrong price</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Incorrect origin address sent to Kuebix. Freight quotes are wrong. Customer receives inaccurate pricing. Trust and margin impact.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Map all warehouse addresses at kickoff with ops team. Define explicit routing rules (which products/regions ship from which warehouse). Test each origin with known Kuebix quotes. Build fallback to default origin if routing is ambiguous.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Consultant + Mike</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>HubSpot CPQ limitations -- no calculated fields, no product variants, no native tax engine</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Workarounds needed for freight as line item (must be pre-computed by n8n). Product selection UX is less polished than dedicated CPQ. Tax calculation requires external logic.</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Pre-compute all calculated values in n8n before quote is published. Use custom properties and filtered views for product selection. Document workaround patterns for admin team. Tax logic in Ops Hub custom code or n8n.</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Consultant</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Kuebix API rate limits undocumented -- high quote volume could hit throttling</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>65 quotes/week (plus revisions) could exceed undocumented rate limits. Freight quotes fail silently or are throttled.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Confirm rate limits with Kuebix support before build begins. Implement response caching for repeat origin/destination/weight combinations (many camp quotes go to similar destinations). Build graceful fallback to manual entry if API is unavailable.</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Consultant</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Adoption risk -- sales reps switching from NetSuite quoting to HubSpot quoting</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Caleb and Don revert to old process because it is familiar. New system goes unused. ROI unrealized.</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Executive mandate from Mike. Show concrete time savings in training (side-by-side demo). 2-week parallel run where both systems are used. Monitor adoption metrics. Caleb is motivated (he described the pain) -- leverage that.</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Mike + Consultant</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Freight class determination per product is unclear or inconsistent</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Wrong freight class sent to Kuebix. Shipping costs are systematically over or under estimated. Margin impact across all quotes.</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Confirm freight class source at kickoff (NetSuite item record field vs. static lookup table vs. calculated from product specs). Document freight class per product line. Validate against known Kuebix quotes for 5 example orders.</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Consultant + Caleb</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Budget authority anchored on Billy $25K verbal benchmark -- $34.5K creates sticker shock</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Patrick (CFO) or Mike expects $25K. $34.5K proposal triggers budget negotiation or scope reduction request.</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Frame $25K as pre-discovery estimate from intro call. Proposal explicitly shows scope expansion since then: Sayer doing all NetSuite work (not TPI), dynamic weight calculation engine, multiple shipping origins, full Kuebix API integration. Value-based ROI framing ($38K-$58K/year savings, 7-9 month payback).</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Kyle + Billy</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>Dynamic weight engine blows past 44 hrs. Fixed fee untenable. Workstream 5 unbounded.</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>RESOLVED 2026-04-04: All 5 Excel files received and validated. No VBA, no external refs, no circular formulas. Dorm Mattress confirmed as highest complexity (9-level nesting, 180+ paths) but within estimate range.</t>
+        </is>
+      </c>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="H15" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1907,633 +2507,601 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Scope Assumptions</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>HubSpot Sales Hub Professional + Commerce Hub Professional (existing)</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Operations Hub Professional recommended (separate license ~$800/mo -- not included in project fee)</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Operations Hub Professional required (separate license ~$800/mo -- enables custom code actions)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Up to 700 products in HubSpot product library (flat catalog, one record per SKU)</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>NetSuite REST API access with OAuth 2.0 M2M credentials provided by client</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Kuebix API credentials (username, API key, 15-character Client ID) provided by client</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>n8n middleware hosted by Sayer or on client infrastructure (hosting cost separate from project fee)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Railway cloud platform for production API hosting (~$5-20/mo -- Phase 2)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Multiple shipping origin addresses -- client provides complete warehouse list with routing rules at kickoff</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Freight class stored as a property per product in NetSuite or as a static lookup per product line</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Up to 30 custom properties across deals, quotes, and line items (overages are change orders)</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>10-12 week implementation timeline</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1: 10-12 weeks | Phase 2: 4-6 weeks (18 weeks total)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>All work conducted remotely</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Rate: $150/hr (internal tracking -- client sees fixed fee only)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Fixed fee: $34,500 -- 5 equal payments of $7,245 ($6,900 + 5% tech/admin fee) every 15 days, Net-15</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Phase 1 fixed fee: ~$30,000 -- 5 payments of $6,300 ($6,000 + 5% tech/admin) every 15 days, Net-15</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 fixed fee: ~$11,500 -- 3 payments of ~$4,027 (~$3,835 + 5% tech/admin) every 15 days, Net-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Dynamic weight calculation covers 5 product lines (Dorm, Camp, Dura-Last, SoFlux OX, Vinyl)</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Excel shipping calculators do not contain VBA macros or external data references (must verify before engagement)</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Excel calculators validated: no VBA, no external refs, no circular formulas (confirmed 2026-04-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Quote template matches current NetSuite format (5 PDF examples as reference)</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>SOW signed by Mike Taylor (VP) or Patrick (CFO) -- budget authority, not just project champion</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>SOW signed by Mike Taylor (VP) or Patrick (CFO) -- budget authority</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Production code delivered as version-controlled codebase (not n8n workflows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Out of Scope</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="n">
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Government RFP automation, compliance tracking, bid management (Phase 2)</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Government RFP automation, compliance tracking, bid management (future phase)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Customer-facing product configurator / guided selling decision tree (Phase 2)</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Customer-facing product configurator / guided selling decision tree (future phase)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>External storefront build (Shopify or HubSpot Commerce -- Phase 3)</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>External storefront build (Shopify or HubSpot Commerce -- future phase)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>VoIP / call capture system selection or integration</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n">
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>5</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>AI lead enrichment from call transcripts</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="n">
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>6</v>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>NetSuite reimplementation, new module deployment, or SuiteScript development</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="n">
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
         <v>7</v>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Ongoing Kuebix TMS administration or carrier management</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n">
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>8</v>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>HubSpot Marketing Hub configuration or marketing automation</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="n">
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>9</v>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Custom self-service pricing portal</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n">
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
         <v>10</v>
       </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Ongoing managed services beyond 2-week hypercare post go-live</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="n">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Ongoing managed services beyond 2-week hypercare per phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
         <v>11</v>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>HubSpot or NetSuite license procurement or tier changes (recommendations provided only)</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>HubSpot or NetSuite license procurement or tier changes (recommendations only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>12</v>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Data migration from external systems beyond NetSuite product catalog sync</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="n">
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
         <v>13</v>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>TPI (NetSuite partner) coordination or management -- Sayer works directly in NetSuite</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="n"/>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>14</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>n8n as production runtime (may be used for prototyping only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Client Responsibilities</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="n">
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
         <v>1</v>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Provide Kuebix API credentials (username, API key, 15-character Client ID)</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="n">
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
         <v>2</v>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Provide NetSuite admin access or create OAuth 2.0 M2M integration record with API permissions</t>
         </is>
       </c>
-      <c r="C37" s="6" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="n">
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
         <v>3</v>
       </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Provide all 5 Excel shipping calculator files for technical review (action item from Mar 23 call)</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="n">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Excel shipping calculator files -- RECEIVED AND VALIDATED (2026-04-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
         <v>4</v>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Provide complete warehouse address list with product/region routing rules</t>
         </is>
       </c>
-      <c r="C39" s="6" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="n">
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
         <v>5</v>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Confirm freight class per product line (or provide lookup reference)</t>
         </is>
       </c>
-      <c r="C40" s="6" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
         <v>6</v>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Designate primary point of contact (Sarah-Beth recommended)</t>
         </is>
       </c>
-      <c r="C41" s="6" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n">
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
         <v>7</v>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Ensure Caleb and Don availability for 2+ UAT sessions during weeks 9-10</t>
         </is>
       </c>
-      <c r="C42" s="6" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n">
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
         <v>8</v>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>SOW signed by Mike Taylor or Patrick (CFO) -- budget authority</t>
         </is>
       </c>
-      <c r="C43" s="6" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="n">
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
         <v>9</v>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Validate 5-10 sample quotes against current NetSuite output during UAT</t>
         </is>
       </c>
-      <c r="C44" s="6" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="n">
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
         <v>10</v>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Provide 5-10 recent quotes with known freight costs for validation testing</t>
         </is>
       </c>
-      <c r="C45" s="6" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="n"/>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>11</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Clarify 'Special Case Check with Delbert' for Dorm Mattress calculator</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>Open Items (Confirm During Kickoff)</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="n">
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
         <v>1</v>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>NetSuite item types in use (InventoryItem vs. AssemblyItem vs. NonInventoryItem)</t>
         </is>
       </c>
-      <c r="C48" s="6" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="n">
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
         <v>2</v>
       </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>NetSuite price level structure (single price list vs. multiple price levels per customer tier)</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="n">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>NetSuite price level structure (single vs. multiple price levels per customer tier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
         <v>3</v>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>Exact number and full street addresses of all shipping warehouses</t>
         </is>
       </c>
-      <c r="C50" s="6" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="n">
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
         <v>4</v>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Routing rules: which products or regions ship from which warehouse</t>
         </is>
       </c>
-      <c r="C51" s="6" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="n">
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
         <v>5</v>
       </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Discount approval thresholds -- is 10% always automatic? Do higher discounts need Mike/Patrick approval?</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="n">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Discount approval thresholds -- is 10% always automatic? Do higher discounts need approval?</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
         <v>6</v>
       </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Credit hold workflow details -- what triggers a hold, who can override, should quote creation be blocked or just flagged?</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="n">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Credit hold workflow details -- what triggers a hold, who can override, block vs. flag?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
         <v>7</v>
       </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Quote validity period (30 days per current NetSuite quotes -- confirm or adjust)</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="n">
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Quote validity period (30 days per current NetSuite quotes -- confirm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
         <v>8</v>
       </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>Whether Excel spreadsheets contain VBA macros or external data references (blocker for weight calc engine)</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="n">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Dorm Mattress: 'Special Case Check with Delbert' -- undocumented business logic for edge cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
         <v>9</v>
       </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>Dimensional data future-proofing -- carriers may require L x W x H per item (affects data model decisions)</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="n">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Dimensional data future-proofing -- carriers may require L x W x H per item</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
         <v>10</v>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Kuebix rate limits and acceptable API call volume (confirm with Kuebix support)</t>
         </is>
       </c>
-      <c r="C57" s="6" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="n">
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
         <v>11</v>
       </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>Operations Hub Professional -- client decision on whether to add this tier</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="n">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Operations Hub Professional -- client decision on adding this tier (required for Phase 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
         <v>12</v>
       </c>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>n8n hosting location -- Sayer infrastructure or client-provided environment</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="n"/>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Railway hosting -- confirm client or Sayer hosts the production API (Phase 2)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/American Bedding - CPQ Discussion/American_Bedding_CPQ_Estimate.xlsx
+++ b/American Bedding - CPQ Discussion/American_Bedding_CPQ_Estimate.xlsx
@@ -95,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -109,11 +109,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -163,6 +191,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -893,15 +923,15 @@
           <t>PHASE 1 (V1): HUBSPOT-NATIVE CPQ</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="8" t="n"/>
-      <c r="G4" s="8" t="n"/>
-      <c r="H4" s="8" t="n"/>
-      <c r="I4" s="8" t="n"/>
-      <c r="J4" s="8" t="n"/>
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="21" t="n"/>
+      <c r="E4" s="21" t="n"/>
+      <c r="F4" s="21" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="21" t="n"/>
+      <c r="I4" s="21" t="n"/>
+      <c r="J4" s="22" t="n"/>
       <c r="K4" s="8" t="n"/>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
@@ -1141,7 +1171,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>HIGHEST-COMPLEXITY WORKSTREAM. Validated 2026-04-04: no VBA, no external refs, no circular formulas. Dorm (HIGH -- 9-level nesting, 180+ paths), Camp (MED -- 48+ paths), Dura-Last (MED -- 12+ paths), SoFlux OX/Vinyl (LOW -- ~80% reuse). Open: 'Special Case Check with Delbert' in Dorm Mattress.</t>
+          <t>HIGHEST-COMPLEXITY WORKSTREAM. Composition architecture: shared utilities (fabricCalc, cubeVolume, coverWeights, packagingCalc) + one module per product line. Each product has unique physics -- no single template. Dorm (HIGH -- 180+ paths, innerspring/foam/batting/cover), Camp (MED -- 48 paths, 4 foam series + fire barrier), Dura-Last (LOW-MED -- 12 paths, poly fiber only), SoFlux OX/Vinyl (LOW -- covers only, ~95% shared base). Validated 2026-04-04: no VBA, no external refs, no circular formulas. Open: 'Special Case Check with Delbert' in Dorm Mattress.</t>
         </is>
       </c>
       <c r="K9" s="9" t="n"/>
@@ -1448,15 +1478,15 @@
           <t>PHASE 2 (V2): RAILWAY PRODUCTION PLATFORM</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
+      <c r="B17" s="21" t="n"/>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="n"/>
+      <c r="I17" s="21" t="n"/>
+      <c r="J17" s="22" t="n"/>
       <c r="K17" s="13" t="n"/>
       <c r="L17" s="13" t="n"/>
       <c r="M17" s="13" t="n"/>
@@ -1549,7 +1579,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Code already exists from Phase 1 -- migration is refactor + test coverage. Dorm Mattress needs ~20 representative test cases covering 80% of paths. SoFlux/Vinyl share ~80% code. Target: 100% coverage for critical paths.</t>
+          <t>Refactor 5 product modules + shared utilities into Railway API. Composition architecture: shared layer (fabricCalc, cubeVolume, coverWeights, packagingCalc) + per-product modules (dormMattress, campMattress, duraLast, sofluxCover, vinylCover). Each product built and tested independently -- no single template. Unit test coverage for all calculation paths. Dorm Mattress sampling strategy for 180+ paths. SoFlux/Vinyl share ~95% of a base cover module.</t>
         </is>
       </c>
       <c r="K19" s="9" t="n"/>

--- a/American Bedding - CPQ Discussion/American_Bedding_CPQ_Estimate.xlsx
+++ b/American Bedding - CPQ Discussion/American_Bedding_CPQ_Estimate.xlsx
@@ -19,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,29 +31,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
+      <color rgb="001F4E79"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00008000"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color rgb="00808080"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -60,14 +95,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DAEEF3"/>
+        <bgColor rgb="00DAEEF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
+        <bgColor rgb="00548235"/>
       </patternFill>
     </fill>
     <fill>
@@ -78,14 +125,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,8 +141,20 @@
         <bgColor rgb="00F4B084"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -109,90 +168,62 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -561,7 +592,7 @@
   <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
@@ -608,17 +639,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Phase 1 (V1): ~$30,000 | Phase 2 (V2): ~$11,500 | Total: ~$41,500</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>~$18,000-$22,000 (reduced scope)</t>
         </is>
@@ -642,17 +673,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Freight Automation</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Full -- Kuebix API with dynamic weight calculation. Multi-carrier LTL rate shopping automated. Phase 1 via HubSpot custom code, Phase 2 migrates to production API for unlimited execution time.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>None or partial -- manual Kuebix entry continues, or NetSuite-side integration (TPI scope).</t>
         </is>
@@ -666,7 +697,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Dynamic engine replicates Excel formula logic for all 5 product lines. Handles custom sizes. Validated: no VBA, no macros, no external refs. Dorm Mattress is highest complexity (9-level nesting, 180+ paths).</t>
+          <t>Modular engine with composition architecture: shared utilities + per-product modules. Each product has unique physics (Dorm: innerspring/foam/batting, Camp: foam series + fire barrier, Dura-Last: poly fiber, SoFlux/Vinyl: covers only). Validated: no VBA, no macros, no external refs.</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -676,17 +707,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>NetSuite Integration</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Bi-directional: product catalog sync, quote-to-estimate creation, estimate-to-sales-order conversion, credit hold check.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Enhanced one-way: quote visibility in HubSpot. No quote creation from HubSpot.</t>
         </is>
@@ -710,17 +741,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>MEDIUM -- 3-system integration. Kuebix API fully reviewed. Excel calculators validated. HubSpot 20s timeout is Phase 1 limitation, eliminated in Phase 2.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>LOW -- simpler scope but does not solve the core pain point (4-system juggling).</t>
         </is>
@@ -744,17 +775,17 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Payback Period</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Phase 1: 6-8 months on labor savings alone</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>12-18 months (visibility value harder to quantify)</t>
         </is>
@@ -778,39 +809,41 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Future Phase Readiness</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Strong foundation for government RFP automation, customer configurator, and external storefront.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Minimal -- future phase would still need to move quoting to HubSpot.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>HubSpot CPQ with hybrid architecture is recommended. The core pain point is 4-system juggling that costs Caleb 10-60 minutes per quote across 65 quotes/week. The alternative (enhanced visibility) does not reduce that workload. The recommended approach eliminates system-jumping entirely, automates freight calculation, and builds the foundation for future phases. Two-phase delivery gets reps quoting in HubSpot fast (Phase 1) then hardens the platform for long-term reliability (Phase 2). The Kuebix API and Excel calculators have both been fully reviewed and validated.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A17:C17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -825,28 +858,28 @@
   <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="65" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Hourly Rate:</t>
         </is>
       </c>
-      <c r="B1" t="n">
+      <c r="B1" s="8" t="n">
         <v>150</v>
       </c>
     </row>
@@ -901,40 +934,40 @@
           <t>Notes / Assumptions</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Actual Hours</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>Actual Cost</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>PHASE 1 (V1): HUBSPOT-NATIVE CPQ</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="21" t="n"/>
-      <c r="G4" s="21" t="n"/>
-      <c r="H4" s="21" t="n"/>
-      <c r="I4" s="21" t="n"/>
-      <c r="J4" s="22" t="n"/>
-      <c r="K4" s="8" t="n"/>
-      <c r="L4" s="8" t="n"/>
-      <c r="M4" s="8" t="n"/>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="11" t="n"/>
+      <c r="L4" s="11" t="n"/>
+      <c r="M4" s="11" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -961,15 +994,15 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="12">
         <f>C5*$B$1</f>
         <v/>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="12">
         <f>D5*$B$1</f>
         <v/>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="12">
         <f>E5*$B$1</f>
         <v/>
       </c>
@@ -978,9 +1011,9 @@
           <t>Commerce Hub Professional confirmed. Standard CPQ config with custom properties for manufacturing context. Approval workflows for discount overrides.</t>
         </is>
       </c>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="9">
+      <c r="K5" s="13" t="n"/>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="13">
         <f>IF(K5="","",K5-E5)</f>
         <v/>
       </c>
@@ -1010,15 +1043,15 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="12">
         <f>C6*$B$1</f>
         <v/>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="12">
         <f>D6*$B$1</f>
         <v/>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="12">
         <f>E6*$B$1</f>
         <v/>
       </c>
@@ -1027,9 +1060,9 @@
           <t>Flat catalog -- one product per SKU. SuiteQL batch queries (1-2 API calls). HubSpot custom code trigger replaces n8n scheduled sync. OAuth 2.0 M2M auth.</t>
         </is>
       </c>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="9">
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13">
         <f>IF(K6="","",K6-E6)</f>
         <v/>
       </c>
@@ -1059,15 +1092,15 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="12">
         <f>C7*$B$1</f>
         <v/>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="12">
         <f>D7*$B$1</f>
         <v/>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="12">
         <f>E7*$B$1</f>
         <v/>
       </c>
@@ -1076,9 +1109,9 @@
           <t>Bi-directional: HubSpot quote -&gt; NetSuite estimate -&gt; sales order -&gt; work order. Credit hold reads AR data. 1.25x ERP adjacency premium (existing integration). HubSpot custom code handles orchestration.</t>
         </is>
       </c>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="9">
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="13">
         <f>IF(K7="","",K7-E7)</f>
         <v/>
       </c>
@@ -1108,15 +1141,15 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="12">
         <f>C8*$B$1</f>
         <v/>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="12">
         <f>D8*$B$1</f>
         <v/>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="12">
         <f>E8*$B$1</f>
         <v/>
       </c>
@@ -1125,9 +1158,9 @@
           <t>Kuebix API fully reviewed (OpenAPI 3.0.2). Basic Auth. quickRate returns multi-carrier quotes. Full street address required. Origin routing for multiple warehouses. persist=false prevents phantom shipments. 20s HubSpot timeout risk for multi-line quotes.</t>
         </is>
       </c>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="9">
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="13">
         <f>IF(K8="","",K8-E8)</f>
         <v/>
       </c>
@@ -1140,7 +1173,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Replicate Excel formula logic in HubSpot custom code for all 5 product lines: Dorm Mattress, Camp Mattress, Dura-Last Poly-Fiber, SoFlux OX Covers, Vinyl Covers. Panel calcs, fabric weight by cover type, foam weight by density/thickness, innerspring weight by size, batting, insulator pad, packaging. Cube volume for LTL/TL determination.</t>
+          <t>Composition architecture: shared utilities (fabricCalc, cubeVolume, coverWeights, packagingCalc) + one module per product line. Dorm Mattress (innerspring + foam + batting + cover), Camp Mattress (foam core + fire barrier), Dura-Last (poly fiber), SoFlux OX/Vinyl (covers only). Each validated cell-by-cell against its Excel file. Cube volume for LTL/TL determination.</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -1157,26 +1190,26 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="12">
         <f>C9*$B$1</f>
         <v/>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="12">
         <f>D9*$B$1</f>
         <v/>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="12">
         <f>E9*$B$1</f>
         <v/>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>HIGHEST-COMPLEXITY WORKSTREAM. Composition architecture: shared utilities (fabricCalc, cubeVolume, coverWeights, packagingCalc) + one module per product line. Each product has unique physics -- no single template. Dorm (HIGH -- 180+ paths, innerspring/foam/batting/cover), Camp (MED -- 48 paths, 4 foam series + fire barrier), Dura-Last (LOW-MED -- 12 paths, poly fiber only), SoFlux OX/Vinyl (LOW -- covers only, ~95% shared base). Validated 2026-04-04: no VBA, no external refs, no circular formulas. Open: 'Special Case Check with Delbert' in Dorm Mattress.</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="9">
+          <t>HIGHEST-COMPLEXITY WORKSTREAM. Composition architecture -- no single template. Each product has unique physics, seam allowances, and construction constants that cannot be derived by analogy. Dorm (HIGH -- 180+ paths, 9-level nesting), Camp (MED -- 48 paths, foam series + fire barrier), Dura-Last (LOW-MED -- 12 paths, poly fiber), SoFlux OX/Vinyl (LOW -- ~95% shared base). Validated 2026-04-04: no VBA, no external refs, no circular formulas. Open: "Special Case Check with Delbert" in Dorm Mattress.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="13" t="n"/>
+      <c r="M9" s="13">
         <f>IF(K9="","",K9-E9)</f>
         <v/>
       </c>
@@ -1206,15 +1239,15 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="12">
         <f>C10*$B$1</f>
         <v/>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="12">
         <f>D10*$B$1</f>
         <v/>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="12">
         <f>E10*$B$1</f>
         <v/>
       </c>
@@ -1223,9 +1256,9 @@
           <t>Reference: 5 NetSuite PDF examples. Must match header/footer, line item format, terms. HubSpot Flow theme supports custom properties. @media print CSS for PDF.</t>
         </is>
       </c>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="9">
+      <c r="K10" s="13" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13">
         <f>IF(K10="","",K10-E10)</f>
         <v/>
       </c>
@@ -1255,26 +1288,26 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="12">
         <f>C11*$B$1</f>
         <v/>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="12">
         <f>D11*$B$1</f>
         <v/>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="12">
         <f>E11*$B$1</f>
         <v/>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Tax may need external service for multi-state. Discount approval thresholds TBD at kickoff. Credit hold is read from NetSuite -- flags but does not hard-block. Fits within HubSpot custom code 20s limit.</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9">
+          <t>Tax may need external service for multi-state. Discount approval thresholds TBD at kickoff. Credit hold reads NetSuite -- flags but does not hard-block. Fits within HubSpot custom code 20s limit.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n"/>
+      <c r="L11" s="13" t="n"/>
+      <c r="M11" s="13">
         <f>IF(K11="","",K11-E11)</f>
         <v/>
       </c>
@@ -1304,15 +1337,15 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="12">
         <f>C12*$B$1</f>
         <v/>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="12">
         <f>D12*$B$1</f>
         <v/>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="12">
         <f>E12*$B$1</f>
         <v/>
       </c>
@@ -1321,9 +1354,9 @@
           <t>2-3 sessions. Emphasis on time savings. Admin guide covers HubSpot custom code monitoring and product sync. Record for onboarding.</t>
         </is>
       </c>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="9">
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13">
         <f>IF(K12="","",K12-E12)</f>
         <v/>
       </c>
@@ -1336,7 +1369,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>E2E integration testing across all 3 systems. Quote accuracy vs. NetSuite examples. Weight calc vs. Excel baselines. Freight vs. manual Kuebix lookups. UAT with Caleb and Don. 2-week hypercare.</t>
+          <t>E2E integration testing across all 3 systems. Quote accuracy vs. NetSuite examples. Weight calc vs. Excel baselines (cell-by-cell per product -- no cross-product shortcuts). Freight vs. manual Kuebix lookups. UAT with Caleb and Don. 2-week hypercare.</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1353,15 +1386,15 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="12">
         <f>C13*$B$1</f>
         <v/>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="12">
         <f>D13*$B$1</f>
         <v/>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="12">
         <f>E13*$B$1</f>
         <v/>
       </c>
@@ -1370,9 +1403,9 @@
           <t>Test matrix: product sync accuracy, weight calc per product line, freight quote accuracy, template rendering, NetSuite estimate creation, SO conversion, credit hold. 2 UAT sessions. Dorm Mattress sampling strategy for 180+ paths.</t>
         </is>
       </c>
-      <c r="K13" s="9" t="n"/>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="9">
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="13">
         <f>IF(K13="","",K13-E13)</f>
         <v/>
       </c>
@@ -1402,15 +1435,15 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="12">
         <f>C14*$B$1</f>
         <v/>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="12">
         <f>D14*$B$1</f>
         <v/>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="12">
         <f>E14*$B$1</f>
         <v/>
       </c>
@@ -1419,77 +1452,77 @@
           <t>~10% of total. Weekly syncs with Sarah-Beth. Milestone reviews at weeks 4, 8, and go-live. All change requests documented.</t>
         </is>
       </c>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="9">
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13">
         <f>IF(K14="","",K14-E14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>PHASE 1 SUBTOTAL</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11">
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="14">
         <f>SUM(C5:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="14">
         <f>SUM(D5:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="14">
         <f>SUM(E5:E14)</f>
         <v/>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="14">
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="16">
         <f>SUM(G5:G14)</f>
         <v/>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="16">
         <f>SUM(H5:H14)</f>
         <v/>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="16">
         <f>SUM(I5:I14)</f>
         <v/>
       </c>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11">
+      <c r="J15" s="15" t="n"/>
+      <c r="K15" s="15">
         <f>SUM(K5:K14)</f>
         <v/>
       </c>
-      <c r="L15" s="11">
+      <c r="L15" s="15">
         <f>SUM(L5:L14)</f>
         <v/>
       </c>
-      <c r="M15" s="11" t="n"/>
+      <c r="M15" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>PHASE 2 (V2): RAILWAY PRODUCTION PLATFORM</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="22" t="n"/>
-      <c r="K17" s="13" t="n"/>
-      <c r="L17" s="13" t="n"/>
-      <c r="M17" s="13" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="n"/>
+      <c r="I17" s="18" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="18" t="n"/>
+      <c r="L17" s="18" t="n"/>
+      <c r="M17" s="18" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1516,26 +1549,26 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="12">
         <f>C18*$B$1</f>
         <v/>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="12">
         <f>D18*$B$1</f>
         <v/>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="12">
         <f>E18*$B$1</f>
         <v/>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Railway provides managed hosting with auto-deploy from git. Node.js or Python runtime. Environment variables for secrets (API keys, OAuth tokens). Health check endpoint for uptime monitoring.</t>
-        </is>
-      </c>
-      <c r="K18" s="9" t="n"/>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="9">
+          <t>Railway provides managed hosting with auto-deploy from git. Node.js or Python runtime. Environment variables for secrets. Health check endpoint for uptime monitoring.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="n"/>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="13">
         <f>IF(K18="","",K18-E18)</f>
         <v/>
       </c>
@@ -1548,7 +1581,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Migrate all 5 product-line calculators from HubSpot custom code to Railway API. Refactor into modular, testable JavaScript/Python modules. Add comprehensive unit test coverage for all calculation paths. Dorm Mattress sampling strategy for 180+ paths.</t>
+          <t>Refactor 5 product modules + shared utilities into Railway API. Composition architecture: shared layer (fabricCalc, cubeVolume, coverWeights, packagingCalc) + per-product modules (dormMattress, campMattress, duraLast, sofluxCover, vinylCover). Each product built and tested independently.</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1565,26 +1598,26 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="12">
         <f>C19*$B$1</f>
         <v/>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="12">
         <f>D19*$B$1</f>
         <v/>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="12">
         <f>E19*$B$1</f>
         <v/>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Refactor 5 product modules + shared utilities into Railway API. Composition architecture: shared layer (fabricCalc, cubeVolume, coverWeights, packagingCalc) + per-product modules (dormMattress, campMattress, duraLast, sofluxCover, vinylCover). Each product built and tested independently -- no single template. Unit test coverage for all calculation paths. Dorm Mattress sampling strategy for 180+ paths. SoFlux/Vinyl share ~95% of a base cover module.</t>
-        </is>
-      </c>
-      <c r="K19" s="9" t="n"/>
-      <c r="L19" s="9" t="n"/>
-      <c r="M19" s="9">
+          <t>Code exists from Phase 1 -- migration is refactor + test coverage. Each module validated cell-by-cell against its own Excel file -- no cross-product shortcuts. Dorm needs ~20 representative test cases for 180+ paths. SoFlux/Vinyl share ~95% code. Target: 100% coverage for critical paths.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13">
         <f>IF(K19="","",K19-E19)</f>
         <v/>
       </c>
@@ -1597,7 +1630,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Migrate Kuebix quickRate orchestration to Railway API. Multi-line, multi-carrier quote assembly without timeout risk. Retry logic for carrier API failures. Response caching for repeat origin/destination/weight combos.</t>
+          <t>Migrate Kuebix quickRate orchestration to Railway API. Multi-line, multi-carrier quote assembly without timeout risk. Retry logic for carrier API failures. Response caching for repeat shipping lanes.</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1614,26 +1647,26 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="12">
         <f>C20*$B$1</f>
         <v/>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="12">
         <f>D20*$B$1</f>
         <v/>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="12">
         <f>E20*$B$1</f>
         <v/>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>Eliminates HubSpot 20s timeout constraint. Retry logic handles intermittent Kuebix API failures gracefully. Cache reduces API calls for repeat shipping lanes.</t>
-        </is>
-      </c>
-      <c r="K20" s="9" t="n"/>
-      <c r="L20" s="9" t="n"/>
-      <c r="M20" s="9">
+          <t>Eliminates HubSpot 20s timeout constraint. Retry logic handles intermittent Kuebix API failures. Cache reduces API calls for repeat lanes.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="n"/>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="13">
         <f>IF(K20="","",K20-E20)</f>
         <v/>
       </c>
@@ -1663,26 +1696,26 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="12">
         <f>C21*$B$1</f>
         <v/>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="12">
         <f>D21*$B$1</f>
         <v/>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="12">
         <f>E21*$B$1</f>
         <v/>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>OAuth 2.0 M2M token refresh automated. SuiteQL catalog extraction runs on schedule (Railway cron). Estimate/SO creation with retry. Full audit logging.</t>
-        </is>
-      </c>
-      <c r="K21" s="9" t="n"/>
-      <c r="L21" s="9" t="n"/>
-      <c r="M21" s="9">
+          <t>OAuth 2.0 M2M token refresh automated. SuiteQL catalog extraction on schedule. Estimate/SO creation with retry. Full audit logging.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="13" t="n"/>
+      <c r="M21" s="13">
         <f>IF(K21="","",K21-E21)</f>
         <v/>
       </c>
@@ -1712,26 +1745,26 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="12">
         <f>C22*$B$1</f>
         <v/>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="12">
         <f>D22*$B$1</f>
         <v/>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="12">
         <f>E22*$B$1</f>
         <v/>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Simple HTTP calls from HubSpot custom code to Railway API. Minimal logic in HubSpot -- just trigger + response handling. Reduces HubSpot custom code complexity significantly.</t>
-        </is>
-      </c>
-      <c r="K22" s="9" t="n"/>
-      <c r="L22" s="9" t="n"/>
-      <c r="M22" s="9">
+          <t>Simple HTTP calls from HubSpot custom code to Railway API. Minimal logic in HubSpot -- just trigger + response handling.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="13">
         <f>IF(K22="","",K22-E22)</f>
         <v/>
       </c>
@@ -1761,15 +1794,15 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="12">
         <f>C23*$B$1</f>
         <v/>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="12">
         <f>D23*$B$1</f>
         <v/>
       </c>
-      <c r="I23" s="3">
+      <c r="I23" s="12">
         <f>E23*$B$1</f>
         <v/>
       </c>
@@ -1778,9 +1811,9 @@
           <t>Regression against Phase 1 baseline ensures zero behavior change. Load test confirms production volume capacity. Updated admin guide and architecture docs.</t>
         </is>
       </c>
-      <c r="K23" s="9" t="n"/>
-      <c r="L23" s="9" t="n"/>
-      <c r="M23" s="9">
+      <c r="K23" s="13" t="n"/>
+      <c r="L23" s="13" t="n"/>
+      <c r="M23" s="13">
         <f>IF(K23="","",K23-E23)</f>
         <v/>
       </c>
@@ -1810,15 +1843,15 @@
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="12">
         <f>C24*$B$1</f>
         <v/>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="12">
         <f>D24*$B$1</f>
         <v/>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="12">
         <f>E24*$B$1</f>
         <v/>
       </c>
@@ -1827,142 +1860,142 @@
           <t>Lighter PM load than Phase 1. ~10% of Phase 2 hours.</t>
         </is>
       </c>
-      <c r="K24" s="9" t="n"/>
-      <c r="L24" s="9" t="n"/>
-      <c r="M24" s="9">
+      <c r="K24" s="13" t="n"/>
+      <c r="L24" s="13" t="n"/>
+      <c r="M24" s="13">
         <f>IF(K24="","",K24-E24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>PHASE 2 SUBTOTAL</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11">
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="14">
         <f>SUM(C18:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="14">
         <f>SUM(D18:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="14">
         <f>SUM(E18:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="14">
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="16">
         <f>SUM(G18:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="16">
         <f>SUM(H18:H24)</f>
         <v/>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="16">
         <f>SUM(I18:I24)</f>
         <v/>
       </c>
-      <c r="J25" s="11" t="n"/>
-      <c r="K25" s="11">
+      <c r="J25" s="15" t="n"/>
+      <c r="K25" s="15">
         <f>SUM(K18:K24)</f>
         <v/>
       </c>
-      <c r="L25" s="11">
+      <c r="L25" s="15">
         <f>SUM(L18:L24)</f>
         <v/>
       </c>
-      <c r="M25" s="11" t="n"/>
+      <c r="M25" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="15">
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="21">
         <f>C15+C25</f>
         <v/>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="21">
         <f>D15+D25</f>
         <v/>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="21">
         <f>E15+E25</f>
         <v/>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="20">
         <f>$B$1</f>
         <v/>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="22">
         <f>G15+G25</f>
         <v/>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="22">
         <f>H15+H25</f>
         <v/>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="22">
         <f>I15+I25</f>
         <v/>
       </c>
-      <c r="J27" s="15" t="n"/>
-      <c r="K27" s="15">
+      <c r="J27" s="20" t="n"/>
+      <c r="K27" s="20">
         <f>K15+K25</f>
         <v/>
       </c>
-      <c r="L27" s="15">
+      <c r="L27" s="20">
         <f>L15+L25</f>
         <v/>
       </c>
-      <c r="M27" s="15" t="n"/>
+      <c r="M27" s="20" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>PHASE 1 FIXED FEE:</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" s="23" t="n">
         <v>30000</v>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J29" s="24" t="inlineStr">
         <is>
           <t>Fixed fee. Client sees this number only -- no hours breakdown in proposal.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>PHASE 2 FIXED FEE:</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="23" t="n">
         <v>11500</v>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" s="24" t="inlineStr">
         <is>
           <t>Fixed fee. Separate SOW or Phase 2 addendum.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>COMBINED FIXED FEE:</t>
         </is>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="26">
         <f>I29+I30</f>
         <v/>
       </c>
@@ -1985,14 +2018,14 @@
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2038,7 +2071,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2046,12 +2079,12 @@
           <t>HubSpot custom code 20-second execution timeout for complex multi-line quotes</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2066,59 +2099,59 @@
           <t>Test with largest known quote configurations in Phase 1. Manual fallback for edge cases. Phase 2 eliminates this risk entirely by migrating to Railway API (no execution limits).</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Consultant</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Open -- Phase 1 risk</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="n">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Excel weight calculator edge cases -- 'Special Case Check with Delbert' in Dorm Mattress</t>
-        </is>
-      </c>
-      <c r="C3" s="17" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Excel weight calculator edge cases -- "Special Case Check with Delbert" in Dorm Mattress</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Undocumented business logic in Dorm Mattress calculator. #VALUE! errors noted. Edge cases may produce incorrect weights for specific configurations.</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Clarify with Caleb/Delbert at kickoff. Build Dorm Mattress calculator first. Sampling strategy for 180+ paths (~20 representative test cases covering 80% of paths). Validate against known weights.</t>
-        </is>
-      </c>
-      <c r="G3" s="17" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Clarify with Caleb/Delbert at kickoff. Build Dorm Mattress calculator first. Sampling strategy for 180+ paths (~20 representative test cases). Validate against known weights.</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Consultant + Caleb</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2126,12 +2159,12 @@
           <t>NetSuite data quality -- SKU duplicates, stale pricing, missing attributes from Jan 2026 launch</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2146,59 +2179,59 @@
           <t>NetSuite item data audit during Week 1. Define cleanup scope before building sync. SuiteQL queries validate data quality before bulk import. Flag items missing required fields.</t>
         </is>
       </c>
-      <c r="G4" s="17" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Consultant + Sarah-Beth</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Scope creep via Vesco/Kaitlynn relationship -- government RFP work creeps into Phase 1</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Informal requests bypass SOW. Government-specific requirements consume hours budgeted for CPQ. Don Reynolds enthusiasm for future phases pulls scope.</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>SOW signed by Mike Taylor or Patrick (budget authority). Phase boundaries iron-clad in SOW. All change requests documented. Weekly hours tracking visible to client.</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Kyle + Mike</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2206,12 +2239,12 @@
           <t>NetSuite still stabilizing (launched Jan 1, 2026) -- API schema changes, TPI updates</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2226,59 +2259,59 @@
           <t>Build against documented REST API (not custom SuiteScript). Version-lock API endpoints. Establish communication channel with TPI for change notifications.</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Consultant</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="n">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Multiple shipping origins -- wrong origin = wrong freight = wrong price</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Incorrect origin address sent to Kuebix. Freight quotes are wrong. Customer receives inaccurate pricing. Trust and margin impact.</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Map all warehouse addresses at kickoff. Define explicit routing rules. Test each origin with known Kuebix quotes. Default origin fallback if routing is ambiguous.</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Consultant + Mike</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2286,12 +2319,12 @@
           <t>HubSpot CPQ limitations -- no calculated fields, no product variants, no native tax engine</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2306,59 +2339,59 @@
           <t>Pre-compute all calculated values in custom code before quote is published. Use custom properties and filtered views for product selection. Tax logic in Ops Hub custom code.</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Consultant</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Kuebix API rate limits undocumented -- high quote volume could hit throttling</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>65 quotes/week plus revisions could exceed undocumented rate limits. Freight quotes fail or are throttled.</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Confirm rate limits with Kuebix support. Implement response caching for repeat shipping lanes (Phase 2). Graceful fallback to manual entry.</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Consultant</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2366,12 +2399,12 @@
           <t>Adoption risk -- sales reps switching from NetSuite quoting to HubSpot quoting</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2386,59 +2419,59 @@
           <t>Executive mandate from Mike. Show concrete time savings in training. 2-week parallel run. Monitor adoption metrics. Caleb is motivated (described the pain).</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Mike + Consultant</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Freight class determination per product is unclear or inconsistent</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Wrong freight class to Kuebix. Shipping costs systematically over or under estimated. Margin impact across all quotes.</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Confirm freight class source at kickoff. Document per product line. Validate against known Kuebix quotes.</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Consultant + Caleb</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="n">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2446,12 +2479,12 @@
           <t>Budget authority anchored on Billy $25K verbal benchmark -- two-phase total of ~$41.5K creates sticker shock</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -2463,64 +2496,64 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Frame $25K as pre-discovery estimate. Phase 1 at ~$30K is closer to anchor than previous $34.5K. Two-phase reduces upfront commitment. Value-based ROI framing: Phase 1 pays back in 6-8 months. Phase 2 is a natural follow-on after reps see value.</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
+          <t>Frame $25K as pre-discovery estimate. Phase 1 at ~$30K is closer to anchor than previous $34.5K. Two-phase reduces upfront commitment. Value-based ROI framing: Phase 1 pays back in 6-8 months.</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Kyle + Billy</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>RESOLVED</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>--</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Excel weight calculator logic more complex than analyzed -- VBA macros, external references, or circular formulas</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>Dynamic weight engine blows past 44 hrs. Fixed fee untenable. Workstream 5 unbounded.</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>RESOLVED 2026-04-04: All 5 Excel files received and validated. No VBA, no external refs, no circular formulas. Dorm Mattress confirmed as highest complexity (9-level nesting, 180+ paths) but within estimate range.</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t>Kyle</t>
         </is>
       </c>
-      <c r="H15" s="19" t="inlineStr">
+      <c r="H15" s="30" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -2537,601 +2570,688 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Scope Assumptions</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>HubSpot Sales Hub Professional + Commerce Hub Professional (existing)</t>
         </is>
       </c>
+      <c r="C2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Operations Hub Professional required (separate license ~$800/mo -- enables custom code actions)</t>
         </is>
       </c>
+      <c r="C3" s="6" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Up to 700 products in HubSpot product library (flat catalog, one record per SKU)</t>
         </is>
       </c>
+      <c r="C4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>NetSuite REST API access with OAuth 2.0 M2M credentials provided by client</t>
         </is>
       </c>
+      <c r="C5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Kuebix API credentials (username, API key, 15-character Client ID) provided by client</t>
         </is>
       </c>
+      <c r="C6" s="6" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Railway cloud platform for production API hosting (~$5-20/mo -- Phase 2)</t>
         </is>
       </c>
+      <c r="C7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Multiple shipping origin addresses -- client provides complete warehouse list with routing rules at kickoff</t>
         </is>
       </c>
+      <c r="C8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Freight class stored as a property per product in NetSuite or as a static lookup per product line</t>
         </is>
       </c>
+      <c r="C9" s="6" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Up to 30 custom properties across deals, quotes, and line items (overages are change orders)</t>
         </is>
       </c>
+      <c r="C10" s="6" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Phase 1: 10-12 weeks | Phase 2: 4-6 weeks (18 weeks total)</t>
         </is>
       </c>
+      <c r="C11" s="6" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>All work conducted remotely</t>
         </is>
       </c>
+      <c r="C12" s="6" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Rate: $150/hr (internal tracking -- client sees fixed fee only)</t>
         </is>
       </c>
+      <c r="C13" s="6" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Phase 1 fixed fee: ~$30,000 -- 5 payments of $6,300 ($6,000 + 5% tech/admin) every 15 days, Net-15</t>
         </is>
       </c>
+      <c r="C14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Phase 2 fixed fee: ~$11,500 -- 3 payments of ~$4,027 (~$3,835 + 5% tech/admin) every 15 days, Net-15</t>
         </is>
       </c>
+      <c r="C15" s="6" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Dynamic weight calculation covers 5 product lines (Dorm, Camp, Dura-Last, SoFlux OX, Vinyl)</t>
         </is>
       </c>
+      <c r="C16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Excel calculators validated: no VBA, no external refs, no circular formulas (confirmed 2026-04-04)</t>
         </is>
       </c>
+      <c r="C17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Weight engine uses composition architecture: shared utilities + per-product modules (not a single template)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Quote template matches current NetSuite format (5 PDF examples as reference)</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>SOW signed by Mike Taylor (VP) or Patrick (CFO) -- budget authority</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Production code delivered as version-controlled codebase (not n8n workflows)</t>
         </is>
       </c>
+      <c r="C21" s="6" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Out of Scope</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Government RFP automation, compliance tracking, bid management (future phase)</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="C24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Customer-facing product configurator / guided selling decision tree (future phase)</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="C25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>External storefront build (Shopify or HubSpot Commerce -- future phase)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="C26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>VoIP / call capture system selection or integration</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="C27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>AI lead enrichment from call transcripts</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="C28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>NetSuite reimplementation, new module deployment, or SuiteScript development</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="C29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Ongoing Kuebix TMS administration or carrier management</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="C30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>HubSpot Marketing Hub configuration or marketing automation</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="C31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Custom self-service pricing portal</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+      <c r="C32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Ongoing managed services beyond 2-week hypercare per phase</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="C33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>HubSpot or NetSuite license procurement or tier changes (recommendations only)</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+      <c r="C34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Data migration from external systems beyond NetSuite product catalog sync</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+      <c r="C35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>TPI (NetSuite partner) coordination or management -- Sayer works directly in NetSuite</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
+      <c r="C36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>n8n as production runtime (may be used for prototyping only)</t>
         </is>
       </c>
+      <c r="C37" s="6" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Client Responsibilities</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Provide Kuebix API credentials (username, API key, 15-character Client ID)</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
+      <c r="C40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Provide NetSuite admin access or create OAuth 2.0 M2M integration record with API permissions</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+      <c r="C41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Excel shipping calculator files -- RECEIVED AND VALIDATED (2026-04-04)</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
+      <c r="C42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>Provide complete warehouse address list with product/region routing rules</t>
         </is>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
+      <c r="C43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Confirm freight class per product line (or provide lookup reference)</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
+      <c r="C44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Designate primary point of contact (Sarah-Beth recommended)</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
+      <c r="C45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Ensure Caleb and Don availability for 2+ UAT sessions during weeks 9-10</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
+      <c r="C46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>SOW signed by Mike Taylor or Patrick (CFO) -- budget authority</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
+      <c r="C47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Validate 5-10 sample quotes against current NetSuite output during UAT</t>
         </is>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
+      <c r="C48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Provide 5-10 recent quotes with known freight costs for validation testing</t>
         </is>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
+      <c r="C49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Clarify 'Special Case Check with Delbert' for Dorm Mattress calculator</t>
-        </is>
-      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Clarify "Special Case Check with Delbert" for Dorm Mattress calculator</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="A51" s="6" t="n"/>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Open Items (Confirm During Kickoff)</t>
         </is>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>NetSuite item types in use (InventoryItem vs. AssemblyItem vs. NonInventoryItem)</t>
         </is>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
+      <c r="C53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>NetSuite price level structure (single vs. multiple price levels per customer tier)</t>
         </is>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
+      <c r="C54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Exact number and full street addresses of all shipping warehouses</t>
         </is>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
+      <c r="C55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Routing rules: which products or regions ship from which warehouse</t>
         </is>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
+      <c r="C56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>Discount approval thresholds -- is 10% always automatic? Do higher discounts need approval?</t>
         </is>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
+      <c r="C57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Credit hold workflow details -- what triggers a hold, who can override, block vs. flag?</t>
         </is>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
+      <c r="C58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>Quote validity period (30 days per current NetSuite quotes -- confirm)</t>
         </is>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
+      <c r="C59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Dorm Mattress: 'Special Case Check with Delbert' -- undocumented business logic for edge cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Dorm Mattress: "Special Case Check with Delbert" -- undocumented business logic for edge cases</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>Dimensional data future-proofing -- carriers may require L x W x H per item</t>
         </is>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
+      <c r="C61" s="6" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Kuebix rate limits and acceptable API call volume (confirm with Kuebix support)</t>
         </is>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
+      <c r="C62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Operations Hub Professional -- client decision on adding this tier (required for Phase 1)</t>
         </is>
       </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
+      <c r="C63" s="6" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Railway hosting -- confirm client or Sayer hosts the production API (Phase 2)</t>
         </is>
       </c>
+      <c r="C64" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
